--- a/optimized_version/metadata/validation_daily_metrics/agus5_validation_daily_metrics.xlsx
+++ b/optimized_version/metadata/validation_daily_metrics/agus5_validation_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45676</v>
       </c>
       <c r="B2" t="n">
-        <v>1.83612064268207</v>
+        <v>1.07337637037354</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7605211701989134</v>
+        <v>0.4445924926087201</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7605211701989134</v>
+        <v>0.4445924926087201</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45677</v>
       </c>
       <c r="B3" t="n">
-        <v>8.573115089059861</v>
+        <v>8.220880006296177</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -500,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0043559307723</v>
+        <v>2.867628583410945</v>
       </c>
       <c r="F3" t="n">
-        <v>4.868119663005428</v>
+        <v>4.747298879217828</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2881024182613593</v>
+        <v>0.3230007662879004</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45678</v>
       </c>
       <c r="B4" t="n">
-        <v>10.55922231727781</v>
+        <v>10.55442412458593</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>3.050552402328203</v>
+        <v>3.033059666666665</v>
       </c>
       <c r="F4" t="n">
-        <v>4.43154175837907</v>
+        <v>4.46660649025551</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5524912011943021</v>
+        <v>0.5453813248715181</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45679</v>
       </c>
       <c r="B5" t="n">
-        <v>2.811042710762057</v>
+        <v>2.670595709443459</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1.155395833333332</v>
+        <v>1.100318750116414</v>
       </c>
       <c r="F5" t="n">
-        <v>1.505607638318617</v>
+        <v>1.369650635365155</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9179308091181402</v>
+        <v>-0.5871900178513312</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45680</v>
       </c>
       <c r="B6" t="n">
-        <v>3.060733287631929</v>
+        <v>2.774412010253222</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1.242604166666667</v>
+        <v>1.126853416666667</v>
       </c>
       <c r="F6" t="n">
-        <v>1.64668508378376</v>
+        <v>1.491775597157239</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5840831922253125</v>
+        <v>-0.3000614483216737</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45681</v>
       </c>
       <c r="B7" t="n">
-        <v>3.405599417594235</v>
+        <v>2.988979277439491</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.392358333333333</v>
+        <v>1.215841666899499</v>
       </c>
       <c r="F7" t="n">
-        <v>1.930836725296087</v>
+        <v>1.578627555647815</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7007970133131871</v>
+        <v>-0.1368960088102278</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45682</v>
       </c>
       <c r="B8" t="n">
-        <v>7.202558755485433</v>
+        <v>6.959917202254657</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2.149072597671797</v>
+        <v>2.058910416356228</v>
       </c>
       <c r="F8" t="n">
-        <v>4.429440479066569</v>
+        <v>4.339748399397682</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5184000896949104</v>
+        <v>0.5377065286147528</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45683</v>
       </c>
       <c r="B9" t="n">
-        <v>6.09648623664801</v>
+        <v>5.582324385728765</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2.530187500000001</v>
+        <v>2.322577083410943</v>
       </c>
       <c r="F9" t="n">
-        <v>4.010648123880751</v>
+        <v>3.905539224794734</v>
       </c>
       <c r="G9" t="n">
-        <v>0.08986971739882843</v>
+        <v>0.1369490171675428</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45684</v>
       </c>
       <c r="B10" t="n">
-        <v>3.779208215803795</v>
+        <v>3.533116697619624</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.617001764338464</v>
+        <v>1.523902833527359</v>
       </c>
       <c r="F10" t="n">
-        <v>2.114692946047337</v>
+        <v>2.000393347496892</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.140349075287027</v>
+        <v>-0.9152293096295765</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45685</v>
       </c>
       <c r="B11" t="n">
-        <v>2.234446368084684</v>
+        <v>1.934325084701693</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9439798046564075</v>
+        <v>0.8189138333721386</v>
       </c>
       <c r="F11" t="n">
-        <v>1.219054199364098</v>
+        <v>1.063393607968257</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2105411883169988</v>
+        <v>0.3992807657068107</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45686</v>
       </c>
       <c r="B12" t="n">
-        <v>3.691423042794881</v>
+        <v>3.266730512499302</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.512883333333335</v>
+        <v>1.340879333566167</v>
       </c>
       <c r="F12" t="n">
-        <v>1.855241911022508</v>
+        <v>1.666107164503873</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.232501725588155</v>
+        <v>-0.8005142945762695</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45687</v>
       </c>
       <c r="B13" t="n">
-        <v>2.869192922015906</v>
+        <v>2.582073576705693</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -760,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.21233686201026</v>
+        <v>1.096481416938304</v>
       </c>
       <c r="F13" t="n">
-        <v>1.560068003753671</v>
+        <v>1.50021492875911</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4198971005426109</v>
+        <v>-0.3130364384932907</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45688</v>
       </c>
       <c r="B14" t="n">
-        <v>4.189236828164256</v>
+        <v>3.865410399894757</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1.747883333333334</v>
+        <v>1.618504167015912</v>
       </c>
       <c r="F14" t="n">
-        <v>2.24457624155678</v>
+        <v>2.157048242463133</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0788864006535327</v>
+        <v>0.1493239861085526</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45689</v>
       </c>
       <c r="B15" t="n">
-        <v>2.697327812002199</v>
+        <v>2.654709897723722</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1.151251126348725</v>
+        <v>1.14033408360497</v>
       </c>
       <c r="F15" t="n">
-        <v>1.427712570536433</v>
+        <v>1.453388225553768</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2582355255253417</v>
+        <v>-0.3038980965368203</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45690</v>
       </c>
       <c r="B16" t="n">
-        <v>7.971645724516943</v>
+        <v>7.791345102531857</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>2.726258333333334</v>
+        <v>2.658717999883585</v>
       </c>
       <c r="F16" t="n">
-        <v>4.727067838118918</v>
+        <v>4.700136898561811</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5795725498525459</v>
+        <v>0.584349402428707</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45691</v>
       </c>
       <c r="B17" t="n">
-        <v>3.644645383859338</v>
+        <v>3.774367328579804</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1.56484343100513</v>
+        <v>1.6068117492239</v>
       </c>
       <c r="F17" t="n">
-        <v>2.184652420640423</v>
+        <v>2.139883023409884</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6804476855113102</v>
+        <v>0.6934104602732873</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45692</v>
       </c>
       <c r="B18" t="n">
-        <v>3.611227733510882</v>
+        <v>3.16372769146866</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -890,13 +890,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1.612794556344922</v>
+        <v>1.422889585855665</v>
       </c>
       <c r="F18" t="n">
-        <v>2.116862853044293</v>
+        <v>2.132834169324076</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6741355066346142</v>
+        <v>-0.6994928552988271</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45693</v>
       </c>
       <c r="B19" t="n">
-        <v>3.242346116581785</v>
+        <v>3.53880173038173</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1.397558972952887</v>
+        <v>1.543696584652708</v>
       </c>
       <c r="F19" t="n">
-        <v>1.96323027703324</v>
+        <v>1.985640011762525</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2856481428112499</v>
+        <v>0.2692468049136313</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45694</v>
       </c>
       <c r="B20" t="n">
-        <v>4.365363712980031</v>
+        <v>4.096023830115284</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1.810262499883584</v>
+        <v>1.716948666627861</v>
       </c>
       <c r="F20" t="n">
-        <v>2.549653079690391</v>
+        <v>2.354691089598623</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1579899974245511</v>
+        <v>0.01233308705162972</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45695</v>
       </c>
       <c r="B21" t="n">
-        <v>3.822803154914129</v>
+        <v>3.633661640268921</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1.655001764377269</v>
+        <v>1.583487499728362</v>
       </c>
       <c r="F21" t="n">
-        <v>1.925962472548555</v>
+        <v>1.903494175036665</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02187115633379799</v>
+        <v>0.04455975890745767</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45696</v>
       </c>
       <c r="B22" t="n">
-        <v>5.298130329763701</v>
+        <v>5.152910294975715</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -994,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>2.202575637989739</v>
+        <v>2.171479166666669</v>
       </c>
       <c r="F22" t="n">
-        <v>2.982595433174448</v>
+        <v>2.838457191051935</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1840228790638896</v>
+        <v>-0.07234886061061796</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45697</v>
       </c>
       <c r="B23" t="n">
-        <v>6.164840088533132</v>
+        <v>5.362144506457156</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2.511957057353855</v>
+        <v>2.177090750155221</v>
       </c>
       <c r="F23" t="n">
-        <v>3.446967720820221</v>
+        <v>3.068933048716918</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7253284021353512</v>
+        <v>-0.3676411730638274</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45698</v>
       </c>
       <c r="B24" t="n">
-        <v>3.277238084703255</v>
+        <v>2.953543385521055</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1.322460735661536</v>
+        <v>1.201405499999998</v>
       </c>
       <c r="F24" t="n">
-        <v>1.722624176795528</v>
+        <v>1.458769164662692</v>
       </c>
       <c r="G24" t="n">
-        <v>0.42513120365889</v>
+        <v>0.5877498627630477</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45699</v>
       </c>
       <c r="B25" t="n">
-        <v>4.217736542806172</v>
+        <v>3.820036793534971</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1.757020833333334</v>
+        <v>1.599298666550254</v>
       </c>
       <c r="F25" t="n">
-        <v>2.242874651245062</v>
+        <v>2.023579923339324</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.7541944572275239</v>
+        <v>-0.427935047525269</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45700</v>
       </c>
       <c r="B26" t="n">
-        <v>4.010568509124909</v>
+        <v>3.47488851832929</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1.605510735661537</v>
+        <v>1.390275000232829</v>
       </c>
       <c r="F26" t="n">
-        <v>1.865718157562122</v>
+        <v>1.638991518995382</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1604341932404346</v>
+        <v>0.3520879175763327</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45701</v>
       </c>
       <c r="B27" t="n">
-        <v>4.298273338623387</v>
+        <v>3.806899239894996</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1.703424999999999</v>
+        <v>1.502493166666666</v>
       </c>
       <c r="F27" t="n">
-        <v>2.092944385321744</v>
+        <v>1.809984124982131</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.119699803084171</v>
+        <v>-0.5852892497643782</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45702</v>
       </c>
       <c r="B28" t="n">
-        <v>3.671560685512017</v>
+        <v>2.965728323005705</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1.429857695343595</v>
+        <v>1.146573333333333</v>
       </c>
       <c r="F28" t="n">
-        <v>1.765443433129703</v>
+        <v>1.506742159966882</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4446226082249429</v>
+        <v>-0.05226390739678388</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45703</v>
       </c>
       <c r="B29" t="n">
-        <v>5.703431139779156</v>
+        <v>5.437033124588738</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>2.175038626348724</v>
+        <v>2.04539075</v>
       </c>
       <c r="F29" t="n">
-        <v>2.555423593883622</v>
+        <v>2.348664849554564</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.225630746025844</v>
+        <v>-0.8800500367541131</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45704</v>
       </c>
       <c r="B30" t="n">
-        <v>5.24190292289734</v>
+        <v>5.232396400316452</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>2.004775695343593</v>
+        <v>1.972406833333331</v>
       </c>
       <c r="F30" t="n">
-        <v>2.421906528813101</v>
+        <v>2.351274637239765</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.8314397317485698</v>
+        <v>-0.7261740927281684</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45705</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1681047413851498</v>
+        <v>0.2405960413856877</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.06871082793843779</v>
+        <v>0.09967783333333458</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06871082793843779</v>
+        <v>0.2112202142772647</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9719165169239575</v>
+        <v>0.7346179375471089</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45706</v>
       </c>
       <c r="B32" t="n">
-        <v>5.14034535339257</v>
+        <v>4.52340187309186</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>2.051718431005131</v>
+        <v>1.803695083333336</v>
       </c>
       <c r="F32" t="n">
-        <v>2.467660968489775</v>
+        <v>2.205373279533462</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.223104351559643</v>
+        <v>-0.7756324849855312</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45707</v>
       </c>
       <c r="B33" t="n">
-        <v>3.382633289851829</v>
+        <v>2.997624627692162</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1.372</v>
+        <v>1.214921000116415</v>
       </c>
       <c r="F33" t="n">
-        <v>1.656603813951345</v>
+        <v>1.445127101223759</v>
       </c>
       <c r="G33" t="n">
-        <v>0.03072471161627099</v>
+        <v>0.2623982845104037</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45708</v>
       </c>
       <c r="B34" t="n">
-        <v>2.972994972134809</v>
+        <v>2.831912488972849</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>1.259070833333333</v>
+        <v>1.204893166472642</v>
       </c>
       <c r="F34" t="n">
-        <v>1.530153647242638</v>
+        <v>1.434972937367945</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.6565036692966817</v>
+        <v>-0.4568328974418103</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45709</v>
       </c>
       <c r="B35" t="n">
-        <v>4.24869194251975</v>
+        <v>3.688010437746602</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1.745252890687186</v>
+        <v>1.516052083566162</v>
       </c>
       <c r="F35" t="n">
-        <v>2.169076543623359</v>
+        <v>1.897509367804489</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.09934579770538798</v>
+        <v>0.1586970299943139</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45710</v>
       </c>
       <c r="B36" t="n">
-        <v>2.996121082640737</v>
+        <v>2.664105254967782</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.226066666666666</v>
+        <v>1.086819500000002</v>
       </c>
       <c r="F36" t="n">
-        <v>1.896508189913456</v>
+        <v>1.576291290097214</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.194166769386558</v>
+        <v>-0.5157694163008015</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45711</v>
       </c>
       <c r="B37" t="n">
-        <v>5.053459830767308</v>
+        <v>4.666304879976811</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1.866475637989739</v>
+        <v>1.703860583333333</v>
       </c>
       <c r="F37" t="n">
-        <v>2.525761848884641</v>
+        <v>2.520515654130618</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4476239741991882</v>
+        <v>0.4499162430940509</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45712</v>
       </c>
       <c r="B38" t="n">
-        <v>2.848249664427632</v>
+        <v>2.55852776034815</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>1.197128528676926</v>
+        <v>1.078065333449747</v>
       </c>
       <c r="F38" t="n">
-        <v>1.463238209288746</v>
+        <v>1.333410272980471</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.4037255210409336</v>
+        <v>-0.1656810135009721</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45713</v>
       </c>
       <c r="B39" t="n">
-        <v>4.379444054934226</v>
+        <v>4.512960643843783</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1.579987500000001</v>
+        <v>1.606382583333333</v>
       </c>
       <c r="F39" t="n">
-        <v>2.176431168501799</v>
+        <v>2.254149341787754</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3897968350781893</v>
+        <v>0.3454392596935671</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45714</v>
       </c>
       <c r="B40" t="n">
-        <v>3.60601090892851</v>
+        <v>3.283707667367403</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>1.407529166666665</v>
+        <v>1.263595250116415</v>
       </c>
       <c r="F40" t="n">
-        <v>1.848857510838434</v>
+        <v>1.725771527673799</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7135607964094145</v>
+        <v>0.750430118446157</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45715</v>
       </c>
       <c r="B41" t="n">
-        <v>2.946000124223496</v>
+        <v>2.680994512913513</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1.202945833333333</v>
+        <v>1.094157166666666</v>
       </c>
       <c r="F41" t="n">
-        <v>1.700069841851159</v>
+        <v>1.586217789080574</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.8144436137383451</v>
+        <v>-0.5795580164993677</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>2.611804736476109</v>
+        <v>2.381807328451416</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>1.087410735661536</v>
+        <v>0.9925028333333324</v>
       </c>
       <c r="F42" t="n">
-        <v>1.401559614821093</v>
+        <v>1.21854716521397</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.2301474495070857</v>
+        <v>0.07013755520367682</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45717</v>
       </c>
       <c r="B43" t="n">
-        <v>3.571841396905043</v>
+        <v>3.368741476265501</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1.518242942646144</v>
+        <v>1.442900166783081</v>
       </c>
       <c r="F43" t="n">
-        <v>1.780607893012917</v>
+        <v>1.678487197352438</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1370644931572595</v>
+        <v>0.2332075699223467</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45718</v>
       </c>
       <c r="B44" t="n">
-        <v>2.198260291624509</v>
+        <v>2.302314513477753</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9681392643384639</v>
+        <v>1.021112499107483</v>
       </c>
       <c r="F44" t="n">
-        <v>1.178661320337234</v>
+        <v>1.272275316027013</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.3905231741327835</v>
+        <v>-0.6201766557489727</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45719</v>
       </c>
       <c r="B45" t="n">
-        <v>3.801821908258797</v>
+        <v>3.829345377164701</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1.674989902328203</v>
+        <v>1.702018749805974</v>
       </c>
       <c r="F45" t="n">
-        <v>2.102088060963773</v>
+        <v>2.08264334315914</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.9520184643161713</v>
+        <v>-0.9160724003274887</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45720</v>
       </c>
       <c r="B46" t="n">
-        <v>4.739163853732758</v>
+        <v>4.328348376248795</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>1.985697597671797</v>
+        <v>1.825014750271635</v>
       </c>
       <c r="F46" t="n">
-        <v>2.565238246625323</v>
+        <v>2.306952647332895</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.5350101537299758</v>
+        <v>-0.2414613409866284</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45721</v>
       </c>
       <c r="B47" t="n">
-        <v>3.224947680599732</v>
+        <v>2.978211352724363</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1.267403040317945</v>
+        <v>1.169670833333335</v>
       </c>
       <c r="F47" t="n">
-        <v>1.825600140718672</v>
+        <v>1.687642918468835</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.9664347151946271</v>
+        <v>-0.6804644686805013</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45722</v>
       </c>
       <c r="B48" t="n">
-        <v>4.103319882844744</v>
+        <v>3.545514208741797</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1.674001126348725</v>
+        <v>1.443081083333334</v>
       </c>
       <c r="F48" t="n">
-        <v>2.073232765392114</v>
+        <v>1.767747948622533</v>
       </c>
       <c r="G48" t="n">
-        <v>-1.06902544053739</v>
+        <v>-0.5042166342986163</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45723</v>
       </c>
       <c r="B49" t="n">
-        <v>5.920822977704781</v>
+        <v>5.540587458529935</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2.274291028676927</v>
+        <v>2.128111166783082</v>
       </c>
       <c r="F49" t="n">
-        <v>3.730011040159867</v>
+        <v>3.552465461738951</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1487949982439577</v>
+        <v>0.2278998071133087</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45724</v>
       </c>
       <c r="B50" t="n">
-        <v>4.826944177575426</v>
+        <v>4.050668669896335</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1.983483333333332</v>
+        <v>1.6647585</v>
       </c>
       <c r="F50" t="n">
-        <v>2.367375556562811</v>
+        <v>1.982892373832983</v>
       </c>
       <c r="G50" t="n">
-        <v>-1.50106233723517</v>
+        <v>-0.7546418479769832</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45725</v>
       </c>
       <c r="B51" t="n">
-        <v>3.329759927955148</v>
+        <v>2.842203040188159</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1.352613137989741</v>
+        <v>1.161042416783084</v>
       </c>
       <c r="F51" t="n">
-        <v>1.645512401986052</v>
+        <v>1.497503205544778</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.2495701356996818</v>
+        <v>-0.03488916224929084</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45726</v>
       </c>
       <c r="B52" t="n">
-        <v>3.818866540923466</v>
+        <v>3.474737190339291</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1.537491666666667</v>
+        <v>1.396374416783085</v>
       </c>
       <c r="F52" t="n">
-        <v>1.987431891271862</v>
+        <v>1.785794690617619</v>
       </c>
       <c r="G52" t="n">
-        <v>-1.138213082130068</v>
+        <v>-0.726352699851303</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45727</v>
       </c>
       <c r="B53" t="n">
-        <v>4.378235083166685</v>
+        <v>4.006132589959557</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>1.739643431005131</v>
+        <v>1.581261000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>2.170348519303342</v>
+        <v>1.943211800018978</v>
       </c>
       <c r="G53" t="n">
-        <v>-1.163489487529586</v>
+        <v>-0.7343474596563013</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45728</v>
       </c>
       <c r="B54" t="n">
-        <v>5.938504404160483</v>
+        <v>5.625609861594322</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>2.236376764338463</v>
+        <v>2.095864416666667</v>
       </c>
       <c r="F54" t="n">
-        <v>3.104876794372363</v>
+        <v>3.053525061457796</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.396287849519708</v>
+        <v>-0.3504832232102288</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45729</v>
       </c>
       <c r="B55" t="n">
-        <v>5.324825746623381</v>
+        <v>4.923515321300428</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>2.063589902367009</v>
+        <v>1.888745832984089</v>
       </c>
       <c r="F55" t="n">
-        <v>2.410664084628213</v>
+        <v>2.266505104022829</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.3541422562138881</v>
+        <v>-0.1970279695217094</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45730</v>
       </c>
       <c r="B56" t="n">
-        <v>5.037017294910108</v>
+        <v>4.024469324967254</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1.907579166395032</v>
+        <v>1.498434669072584</v>
       </c>
       <c r="F56" t="n">
-        <v>2.331433318774916</v>
+        <v>1.937255160200157</v>
       </c>
       <c r="G56" t="n">
-        <v>-1.361660292903438</v>
+        <v>-0.6305911582745025</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45731</v>
       </c>
       <c r="B57" t="n">
-        <v>5.524723154024224</v>
+        <v>4.64124796512622</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>2.226989899611844</v>
+        <v>1.866716663911502</v>
       </c>
       <c r="F57" t="n">
-        <v>2.630273447827544</v>
+        <v>2.254897885591962</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.1583989765819687</v>
+        <v>0.1486461149752455</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45732</v>
       </c>
       <c r="B58" t="n">
-        <v>5.25325754869772</v>
+        <v>4.999993007216204</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>1.980828526697867</v>
+        <v>1.859328416977106</v>
       </c>
       <c r="F58" t="n">
-        <v>2.363727242059199</v>
+        <v>2.227041638326887</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.9102138886924049</v>
+        <v>-0.6956802090399905</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45733</v>
       </c>
       <c r="B59" t="n">
-        <v>5.768382726279039</v>
+        <v>6.694519331429914</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>2.130243430655884</v>
+        <v>2.433750584225849</v>
       </c>
       <c r="F59" t="n">
-        <v>2.581163716600896</v>
+        <v>2.842018564777006</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.07698245737046028</v>
+        <v>-0.3056637512816018</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45734</v>
       </c>
       <c r="B60" t="n">
-        <v>3.836807211989353</v>
+        <v>3.490302126306223</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>1.512429166627862</v>
+        <v>1.370333917792013</v>
       </c>
       <c r="F60" t="n">
-        <v>1.80630074620071</v>
+        <v>1.619685157193385</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.7286546758144832</v>
+        <v>-0.3899184735593604</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45735</v>
       </c>
       <c r="B61" t="n">
-        <v>5.461453844086002</v>
+        <v>4.93291904167388</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>2.102244086495974</v>
+        <v>1.879855903666956</v>
       </c>
       <c r="F61" t="n">
-        <v>2.560052747621602</v>
+        <v>2.281175932527941</v>
       </c>
       <c r="G61" t="n">
-        <v>-1.119216247488338</v>
+        <v>-0.6826547253582969</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45736</v>
       </c>
       <c r="B62" t="n">
-        <v>4.634182788331484</v>
+        <v>5.454097750573396</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>1.49401313806735</v>
+        <v>1.762760417636794</v>
       </c>
       <c r="F62" t="n">
-        <v>1.878714136111185</v>
+        <v>2.292614773308487</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.081554249454034</v>
+        <v>-0.610605118349375</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45737</v>
       </c>
       <c r="B63" t="n">
-        <v>3.912827237996217</v>
+        <v>4.562544839864694</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1.307046956267208</v>
+        <v>1.520602044993886</v>
       </c>
       <c r="F63" t="n">
-        <v>1.602600487546806</v>
+        <v>1.860920812701718</v>
       </c>
       <c r="G63" t="n">
-        <v>0.2928491158445462</v>
+        <v>0.04650738464216997</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45738</v>
       </c>
       <c r="B64" t="n">
-        <v>5.115782006059503</v>
+        <v>5.208345619733429</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1.595964902677449</v>
+        <v>1.6242</v>
       </c>
       <c r="F64" t="n">
-        <v>1.978239120389981</v>
+        <v>2.024945774628343</v>
       </c>
       <c r="G64" t="n">
-        <v>0.2623675740411245</v>
+        <v>0.2271250637172046</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45739</v>
       </c>
       <c r="B65" t="n">
-        <v>4.837282326481017</v>
+        <v>4.861875639901254</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1.866981558595104</v>
+        <v>1.840633333061698</v>
       </c>
       <c r="F65" t="n">
-        <v>2.402197141233615</v>
+        <v>2.314534216627715</v>
       </c>
       <c r="G65" t="n">
-        <v>0.4093111039701095</v>
+        <v>0.4516362643511618</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45740</v>
       </c>
       <c r="B66" t="n">
-        <v>2.697751862694544</v>
+        <v>2.736878182826903</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>1.071616028715732</v>
+        <v>1.085841667442767</v>
       </c>
       <c r="F66" t="n">
-        <v>1.5554818469347</v>
+        <v>1.430126172274262</v>
       </c>
       <c r="G66" t="n">
-        <v>0.6446735644037255</v>
+        <v>0.6996370684684776</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45741</v>
       </c>
       <c r="B67" t="n">
-        <v>7.994909354175109</v>
+        <v>8.236491784301787</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>1.79866843116035</v>
+        <v>1.845377084691512</v>
       </c>
       <c r="F67" t="n">
-        <v>3.856302576911232</v>
+        <v>3.974766709795524</v>
       </c>
       <c r="G67" t="n">
-        <v>0.7657298281601271</v>
+        <v>0.7511153693597508</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45742</v>
       </c>
       <c r="B68" t="n">
-        <v>6.227581347185588</v>
+        <v>5.697475454674795</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>1.553460735661537</v>
+        <v>1.396335416666667</v>
       </c>
       <c r="F68" t="n">
-        <v>2.127633847576247</v>
+        <v>1.949811617636646</v>
       </c>
       <c r="G68" t="n">
-        <v>0.8999914066186118</v>
+        <v>0.916009755590561</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45743</v>
       </c>
       <c r="B69" t="n">
-        <v>5.39336761610282</v>
+        <v>5.399776280798949</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1.525623873651276</v>
+        <v>1.521299999999998</v>
       </c>
       <c r="F69" t="n">
-        <v>3.55962199104463</v>
+        <v>3.574421481192213</v>
       </c>
       <c r="G69" t="n">
-        <v>0.6757329157046671</v>
+        <v>0.6730309638286258</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45744</v>
       </c>
       <c r="B70" t="n">
-        <v>3.632931382660878</v>
+        <v>3.566100475276127</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>1.263300000000001</v>
+        <v>1.224895833333333</v>
       </c>
       <c r="F70" t="n">
-        <v>1.713326361714627</v>
+        <v>1.600162215149346</v>
       </c>
       <c r="G70" t="n">
-        <v>0.5340916035587582</v>
+        <v>0.5936049913649251</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45745</v>
       </c>
       <c r="B71" t="n">
-        <v>4.022163580014924</v>
+        <v>4.81611806266111</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1.50320593100513</v>
+        <v>1.782972166666665</v>
       </c>
       <c r="F71" t="n">
-        <v>2.23667393454487</v>
+        <v>2.435881509885281</v>
       </c>
       <c r="G71" t="n">
-        <v>-1.344875592355524</v>
+        <v>-1.781165096949862</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45746</v>
       </c>
       <c r="B72" t="n">
-        <v>5.918866823092437</v>
+        <v>4.656098785460113</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>2.289979166666667</v>
+        <v>1.782123333333333</v>
       </c>
       <c r="F72" t="n">
-        <v>2.732344783176564</v>
+        <v>2.294532808835747</v>
       </c>
       <c r="G72" t="n">
-        <v>-1.688378933086985</v>
+        <v>-0.8958676967009136</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45747</v>
       </c>
       <c r="B73" t="n">
-        <v>4.758152103463456</v>
+        <v>4.216960527444166</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1.916986862010261</v>
+        <v>1.693373666899499</v>
       </c>
       <c r="F73" t="n">
-        <v>2.285777689789065</v>
+        <v>2.02888951481646</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.3561906315588097</v>
+        <v>-0.06848777228090741</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45748</v>
       </c>
       <c r="B74" t="n">
-        <v>2.336687321639134</v>
+        <v>2.094800744203067</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9399017643384635</v>
+        <v>0.8397596666666652</v>
       </c>
       <c r="F74" t="n">
-        <v>1.269351402564804</v>
+        <v>1.079737658327861</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.6149895850447611</v>
+        <v>-0.1685370553208216</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45749</v>
       </c>
       <c r="B75" t="n">
-        <v>6.218571172567114</v>
+        <v>6.208284581481155</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>1.396047597671797</v>
+        <v>1.374792249999999</v>
       </c>
       <c r="F75" t="n">
-        <v>3.866406139701178</v>
+        <v>3.900309022017505</v>
       </c>
       <c r="G75" t="n">
-        <v>0.7875874473494892</v>
+        <v>0.7838460034756011</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45750</v>
       </c>
       <c r="B76" t="n">
-        <v>2.772864431633739</v>
+        <v>2.608903678095088</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.5861815689948698</v>
+        <v>0.5481416666666669</v>
       </c>
       <c r="F76" t="n">
-        <v>0.7154103999866085</v>
+        <v>0.6841456478703933</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.04684192629017936</v>
+        <v>0.04265660212211331</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45751</v>
       </c>
       <c r="B77" t="n">
-        <v>2.909058706177028</v>
+        <v>2.818738488922325</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0.6046624999999994</v>
+        <v>0.5812791666666661</v>
       </c>
       <c r="F77" t="n">
-        <v>0.7809267349952066</v>
+        <v>0.767399818923182</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.4220538614764253</v>
+        <v>-0.3732159794796839</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45752</v>
       </c>
       <c r="B78" t="n">
-        <v>4.451707147520149</v>
+        <v>4.039799477010487</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9324732356615364</v>
+        <v>0.8402624999999997</v>
       </c>
       <c r="F78" t="n">
-        <v>1.108669118803774</v>
+        <v>1.001434111869905</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.8525485808057993</v>
+        <v>-0.5115080537644374</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45753</v>
       </c>
       <c r="B79" t="n">
-        <v>4.668414928598769</v>
+        <v>3.844487558494216</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9731559310051301</v>
+        <v>0.7982666666666663</v>
       </c>
       <c r="F79" t="n">
-        <v>1.187725515233495</v>
+        <v>1.012218590111181</v>
       </c>
       <c r="G79" t="n">
-        <v>-1.268115182062983</v>
+        <v>-0.6473335801793842</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45754</v>
       </c>
       <c r="B80" t="n">
-        <v>4.240326919391361</v>
+        <v>3.8975841042618</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.8744815689948694</v>
+        <v>0.8003249999999998</v>
       </c>
       <c r="F80" t="n">
-        <v>1.09339842106144</v>
+        <v>1.027920861901992</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.2464186745976269</v>
+        <v>-0.1016063304256527</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45755</v>
       </c>
       <c r="B81" t="n">
-        <v>5.049430022125235</v>
+        <v>5.060937370368344</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>1.058626764338463</v>
+        <v>1.058875</v>
       </c>
       <c r="F81" t="n">
-        <v>1.3796968018206</v>
+        <v>1.323128103838274</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.7252433580718247</v>
+        <v>-0.5866708287834661</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45756</v>
       </c>
       <c r="B82" t="n">
-        <v>3.584053483525065</v>
+        <v>3.192268696125719</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0.7853892643384635</v>
+        <v>0.7005916666666662</v>
       </c>
       <c r="F82" t="n">
-        <v>1.030969365728942</v>
+        <v>0.8883401502240005</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.5014151508977456</v>
+        <v>-0.1147252922151563</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45757</v>
       </c>
       <c r="B83" t="n">
-        <v>4.220548296380155</v>
+        <v>3.929034636174562</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0.9298679789645512</v>
+        <v>0.8677347826086954</v>
       </c>
       <c r="F83" t="n">
-        <v>1.170031256533086</v>
+        <v>1.105624265330205</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.8515216860782302</v>
+        <v>-0.6532898478675766</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>

--- a/optimized_version/metadata/validation_daily_metrics/agus5_validation_daily_metrics.xlsx
+++ b/optimized_version/metadata/validation_daily_metrics/agus5_validation_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45676</v>
       </c>
       <c r="B2" t="n">
-        <v>1.07337637037354</v>
+        <v>1.983220666344741</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4445924926087201</v>
+        <v>0.8214499999999916</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4445924926087201</v>
+        <v>0.8214499999999916</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45677</v>
       </c>
       <c r="B3" t="n">
-        <v>8.220880006296177</v>
+        <v>8.145559215752417</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -500,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2.867628583410945</v>
+        <v>2.851618749495535</v>
       </c>
       <c r="F3" t="n">
-        <v>4.747298879217828</v>
+        <v>4.702082761742061</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3230007662879004</v>
+        <v>0.335835642537005</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45678</v>
       </c>
       <c r="B4" t="n">
-        <v>10.55442412458593</v>
+        <v>10.30801747924218</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>3.033059666666665</v>
+        <v>2.957709666162202</v>
       </c>
       <c r="F4" t="n">
-        <v>4.46660649025551</v>
+        <v>4.411554951181254</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5453813248715181</v>
+        <v>0.5565187395433193</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45679</v>
       </c>
       <c r="B5" t="n">
-        <v>2.670595709443459</v>
+        <v>2.698559484833133</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1.100318750116414</v>
+        <v>1.110943749650752</v>
       </c>
       <c r="F5" t="n">
-        <v>1.369650635365155</v>
+        <v>1.406788651626623</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5871900178513312</v>
+        <v>-0.6744301269474964</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45680</v>
       </c>
       <c r="B6" t="n">
-        <v>2.774412010253222</v>
+        <v>2.986931666417381</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1.126853416666667</v>
+        <v>1.214700749650755</v>
       </c>
       <c r="F6" t="n">
-        <v>1.491775597157239</v>
+        <v>1.539311919584768</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3000614483216737</v>
+        <v>-0.3842360246237526</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45681</v>
       </c>
       <c r="B7" t="n">
-        <v>2.988979277439491</v>
+        <v>2.902551086378173</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.215841666899499</v>
+        <v>1.180627667015914</v>
       </c>
       <c r="F7" t="n">
-        <v>1.578627555647815</v>
+        <v>1.611453591957102</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1368960088102278</v>
+        <v>-0.1846689037308429</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45682</v>
       </c>
       <c r="B8" t="n">
-        <v>6.959917202254657</v>
+        <v>7.205158908426992</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2.058910416356228</v>
+        <v>2.129803583682581</v>
       </c>
       <c r="F8" t="n">
-        <v>4.339748399397682</v>
+        <v>4.475526189891363</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5377065286147528</v>
+        <v>0.5083264306941658</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45683</v>
       </c>
       <c r="B9" t="n">
-        <v>5.582324385728765</v>
+        <v>5.552384502685806</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2.322577083410943</v>
+        <v>2.312172917015914</v>
       </c>
       <c r="F9" t="n">
-        <v>3.905539224794734</v>
+        <v>3.885312233260676</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1369490171675428</v>
+        <v>0.1458654401034152</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45684</v>
       </c>
       <c r="B10" t="n">
-        <v>3.533116697619624</v>
+        <v>3.577043114371809</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.523902833527359</v>
+        <v>1.542248667171132</v>
       </c>
       <c r="F10" t="n">
-        <v>2.000393347496892</v>
+        <v>1.991992999532289</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9152293096295765</v>
+        <v>-0.8991776547361152</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45685</v>
       </c>
       <c r="B11" t="n">
-        <v>1.934325084701693</v>
+        <v>1.932218276923399</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8189138333721386</v>
+        <v>0.8190596670159129</v>
       </c>
       <c r="F11" t="n">
-        <v>1.063393607968257</v>
+        <v>1.084504713001423</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3992807657068107</v>
+        <v>0.3751923558566331</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45686</v>
       </c>
       <c r="B12" t="n">
-        <v>3.266730512499302</v>
+        <v>3.389433198437521</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.340879333566167</v>
+        <v>1.391229333682581</v>
       </c>
       <c r="F12" t="n">
-        <v>1.666107164503873</v>
+        <v>1.673898943326144</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8005142945762695</v>
+        <v>-0.8173943779349986</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45687</v>
       </c>
       <c r="B13" t="n">
-        <v>2.582073576705693</v>
+        <v>2.559285327242081</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -760,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.096481416938304</v>
+        <v>1.083677249495535</v>
       </c>
       <c r="F13" t="n">
-        <v>1.50021492875911</v>
+        <v>1.407409463558369</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3130364384932907</v>
+        <v>-0.1556085507660341</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45688</v>
       </c>
       <c r="B14" t="n">
-        <v>3.865410399894757</v>
+        <v>3.70591113678375</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1.618504167015912</v>
+        <v>1.552662500504465</v>
       </c>
       <c r="F14" t="n">
-        <v>2.157048242463133</v>
+        <v>2.092252552983187</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1493239861085526</v>
+        <v>0.1996633891417962</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45689</v>
       </c>
       <c r="B15" t="n">
-        <v>2.654709897723722</v>
+        <v>2.567214034636101</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1.14033408360497</v>
+        <v>1.101857582984087</v>
       </c>
       <c r="F15" t="n">
-        <v>1.453388225553768</v>
+        <v>1.487569630134863</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3038980965368203</v>
+        <v>-0.3659505678080257</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45690</v>
       </c>
       <c r="B16" t="n">
-        <v>7.791345102531857</v>
+        <v>7.828767811773495</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>2.658717999883585</v>
+        <v>2.661434667171134</v>
       </c>
       <c r="F16" t="n">
-        <v>4.700136898561811</v>
+        <v>4.718634134887041</v>
       </c>
       <c r="G16" t="n">
-        <v>0.584349402428707</v>
+        <v>0.5810714059797735</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45691</v>
       </c>
       <c r="B17" t="n">
-        <v>3.774367328579804</v>
+        <v>3.52865955703171</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6068117492239</v>
+        <v>1.506386749650754</v>
       </c>
       <c r="F17" t="n">
-        <v>2.139883023409884</v>
+        <v>2.088551541117603</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6934104602732873</v>
+        <v>0.7079429721495603</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45692</v>
       </c>
       <c r="B18" t="n">
-        <v>3.16372769146866</v>
+        <v>3.186278439755164</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -890,13 +890,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1.422889585855665</v>
+        <v>1.432947917171131</v>
       </c>
       <c r="F18" t="n">
-        <v>2.132834169324076</v>
+        <v>2.159480548052298</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6994928552988271</v>
+        <v>-0.7422230544833717</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45693</v>
       </c>
       <c r="B19" t="n">
-        <v>3.53880173038173</v>
+        <v>3.48764802826862</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1.543696584652708</v>
+        <v>1.520315917171132</v>
       </c>
       <c r="F19" t="n">
-        <v>1.985640011762525</v>
+        <v>2.06178877331135</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2692468049136313</v>
+        <v>0.2121237069630448</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45694</v>
       </c>
       <c r="B20" t="n">
-        <v>4.096023830115284</v>
+        <v>3.926766662680479</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1.716948666627861</v>
+        <v>1.643965333837798</v>
       </c>
       <c r="F20" t="n">
-        <v>2.354691089598623</v>
+        <v>2.300297200577154</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01233308705162972</v>
+        <v>0.05743669961201592</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45695</v>
       </c>
       <c r="B21" t="n">
-        <v>3.633661640268921</v>
+        <v>3.500772267891948</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1.583487499728362</v>
+        <v>1.524406832828866</v>
       </c>
       <c r="F21" t="n">
-        <v>1.903494175036665</v>
+        <v>1.835403712971078</v>
       </c>
       <c r="G21" t="n">
-        <v>0.04455975890745767</v>
+        <v>0.1116918708893692</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45696</v>
       </c>
       <c r="B22" t="n">
-        <v>5.152910294975715</v>
+        <v>5.082510639380375</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -994,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>2.171479166666669</v>
+        <v>2.139706832984087</v>
       </c>
       <c r="F22" t="n">
-        <v>2.838457191051935</v>
+        <v>2.834191317574477</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.07234886061061796</v>
+        <v>-0.06912804960008767</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45697</v>
       </c>
       <c r="B23" t="n">
-        <v>5.362144506457156</v>
+        <v>5.271334921448919</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2.177090750155221</v>
+        <v>2.139657417015912</v>
       </c>
       <c r="F23" t="n">
-        <v>3.068933048716918</v>
+        <v>3.070164327916131</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3676411730638274</v>
+        <v>-0.3687388092181654</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45698</v>
       </c>
       <c r="B24" t="n">
-        <v>2.953543385521055</v>
+        <v>2.804611015242547</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1.201405499999998</v>
+        <v>1.14487066717113</v>
       </c>
       <c r="F24" t="n">
-        <v>1.458769164662692</v>
+        <v>1.360308162777914</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5877498627630477</v>
+        <v>0.6415221981739513</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45699</v>
       </c>
       <c r="B25" t="n">
-        <v>3.820036793534971</v>
+        <v>3.709871792733462</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1.599298666550254</v>
+        <v>1.551501332828867</v>
       </c>
       <c r="F25" t="n">
-        <v>2.023579923339324</v>
+        <v>1.924093892877979</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.427935047525269</v>
+        <v>-0.2909821916661304</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45700</v>
       </c>
       <c r="B26" t="n">
-        <v>3.47488851832929</v>
+        <v>3.621715912588796</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1.390275000232829</v>
+        <v>1.450784832984087</v>
       </c>
       <c r="F26" t="n">
-        <v>1.638991518995382</v>
+        <v>1.696604809167388</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3520879175763327</v>
+        <v>0.305736947180193</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45701</v>
       </c>
       <c r="B27" t="n">
-        <v>3.806899239894996</v>
+        <v>3.583903545071409</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1.502493166666666</v>
+        <v>1.410349999495533</v>
       </c>
       <c r="F27" t="n">
-        <v>1.809984124982131</v>
+        <v>1.737256824451684</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.5852892497643782</v>
+        <v>-0.4604511526419217</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45702</v>
       </c>
       <c r="B28" t="n">
-        <v>2.965728323005705</v>
+        <v>3.031808227235938</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1.146573333333333</v>
+        <v>1.170829000349247</v>
       </c>
       <c r="F28" t="n">
-        <v>1.506742159966882</v>
+        <v>1.492523555291694</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.05226390739678388</v>
+        <v>-0.03249791079970232</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45703</v>
       </c>
       <c r="B29" t="n">
-        <v>5.437033124588738</v>
+        <v>5.32279910336817</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>2.04539075</v>
+        <v>1.9981559161622</v>
       </c>
       <c r="F29" t="n">
-        <v>2.348664849554564</v>
+        <v>2.315501549284515</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.8800500367541131</v>
+        <v>-0.8273320167174587</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45704</v>
       </c>
       <c r="B30" t="n">
-        <v>5.232396400316452</v>
+        <v>5.12881056697656</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1.972406833333331</v>
+        <v>1.930933332828866</v>
       </c>
       <c r="F30" t="n">
-        <v>2.351274637239765</v>
+        <v>2.306870345866708</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.7261740927281684</v>
+        <v>-0.6615914486961916</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45705</v>
       </c>
       <c r="B31" t="n">
-        <v>0.2405960413856877</v>
+        <v>0.5015450144219378</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.09967783333333458</v>
+        <v>0.2053263329840901</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2112202142772647</v>
+        <v>0.2776944180662815</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7346179375471089</v>
+        <v>0.5412934861248364</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45706</v>
       </c>
       <c r="B32" t="n">
-        <v>4.52340187309186</v>
+        <v>4.477735292277905</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1.803695083333336</v>
+        <v>1.784676917171135</v>
       </c>
       <c r="F32" t="n">
-        <v>2.205373279533462</v>
+        <v>2.188515751017505</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.7756324849855312</v>
+        <v>-0.7485909181003489</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45707</v>
       </c>
       <c r="B33" t="n">
-        <v>2.997624627692162</v>
+        <v>2.706091704564952</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1.214921000116415</v>
+        <v>1.094025166162201</v>
       </c>
       <c r="F33" t="n">
-        <v>1.445127101223759</v>
+        <v>1.314212003327263</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2623982845104037</v>
+        <v>0.389984759077144</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45708</v>
       </c>
       <c r="B34" t="n">
-        <v>2.831912488972849</v>
+        <v>2.779155228387157</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>1.204893166472642</v>
+        <v>1.181791666317421</v>
       </c>
       <c r="F34" t="n">
-        <v>1.434972937367945</v>
+        <v>1.398549681949838</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.4568328974418103</v>
+        <v>-0.3838152625217042</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45709</v>
       </c>
       <c r="B35" t="n">
-        <v>3.688010437746602</v>
+        <v>3.647824778921632</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1.516052083566162</v>
+        <v>1.497256250349245</v>
       </c>
       <c r="F35" t="n">
-        <v>1.897509367804489</v>
+        <v>1.853728648840779</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1586970299943139</v>
+        <v>0.1970714721392673</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45710</v>
       </c>
       <c r="B36" t="n">
-        <v>2.664105254967782</v>
+        <v>2.518101995123971</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.086819500000002</v>
+        <v>1.026466833837804</v>
       </c>
       <c r="F36" t="n">
-        <v>1.576291290097214</v>
+        <v>1.482933538248408</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.5157694163008015</v>
+        <v>-0.3415398046607125</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45711</v>
       </c>
       <c r="B37" t="n">
-        <v>4.666304879976811</v>
+        <v>4.702332455290749</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1.703860583333333</v>
+        <v>1.7186814161622</v>
       </c>
       <c r="F37" t="n">
-        <v>2.520515654130618</v>
+        <v>2.549900949347671</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4499162430940509</v>
+        <v>0.4370152326987506</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45712</v>
       </c>
       <c r="B38" t="n">
-        <v>2.55852776034815</v>
+        <v>2.410706690458386</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>1.078065333449747</v>
+        <v>1.015651333837797</v>
       </c>
       <c r="F38" t="n">
-        <v>1.333410272980471</v>
+        <v>1.262539593439431</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.1656810135009721</v>
+        <v>-0.04506220688064166</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45713</v>
       </c>
       <c r="B39" t="n">
-        <v>4.512960643843783</v>
+        <v>4.515743266426927</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1.606382583333333</v>
+        <v>1.603249249495532</v>
       </c>
       <c r="F39" t="n">
-        <v>2.254149341787754</v>
+        <v>2.26599982268645</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3454392596935671</v>
+        <v>0.3385388746746508</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45714</v>
       </c>
       <c r="B40" t="n">
-        <v>3.283707667367403</v>
+        <v>3.260082960173152</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>1.263595250116415</v>
+        <v>1.260431249650753</v>
       </c>
       <c r="F40" t="n">
-        <v>1.725771527673799</v>
+        <v>1.677894641071769</v>
       </c>
       <c r="G40" t="n">
-        <v>0.750430118446157</v>
+        <v>0.7640853299883822</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45715</v>
       </c>
       <c r="B41" t="n">
-        <v>2.680994512913513</v>
+        <v>2.812811961415291</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1.094157166666666</v>
+        <v>1.149298832984087</v>
       </c>
       <c r="F41" t="n">
-        <v>1.586217789080574</v>
+        <v>1.557604591342178</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.5795580164993677</v>
+        <v>-0.5230858632698201</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>2.381807328451416</v>
+        <v>2.038636787078138</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9925028333333324</v>
+        <v>0.8507263336825766</v>
       </c>
       <c r="F42" t="n">
-        <v>1.21854716521397</v>
+        <v>1.110202228888832</v>
       </c>
       <c r="G42" t="n">
-        <v>0.07013755520367682</v>
+        <v>0.2281405774127074</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45717</v>
       </c>
       <c r="B43" t="n">
-        <v>3.368741476265501</v>
+        <v>3.287368455255916</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1.442900166783081</v>
+        <v>1.406582000504464</v>
       </c>
       <c r="F43" t="n">
-        <v>1.678487197352438</v>
+        <v>1.655671938883795</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2332075699223467</v>
+        <v>0.2539115322306903</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45718</v>
       </c>
       <c r="B44" t="n">
-        <v>2.302314513477753</v>
+        <v>2.122270416822106</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1.021112499107483</v>
+        <v>0.9410666671711322</v>
       </c>
       <c r="F44" t="n">
-        <v>1.272275316027013</v>
+        <v>1.23049558556479</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.6201766557489727</v>
+        <v>-0.5155151692770044</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45719</v>
       </c>
       <c r="B45" t="n">
-        <v>3.829345377164701</v>
+        <v>3.567748408236837</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1.702018749805974</v>
+        <v>1.587256249650754</v>
       </c>
       <c r="F45" t="n">
-        <v>2.08264334315914</v>
+        <v>1.993495318382474</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.9160724003274887</v>
+        <v>-0.7555473611282337</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45720</v>
       </c>
       <c r="B46" t="n">
-        <v>4.328348376248795</v>
+        <v>4.374829758794013</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>1.825014750271635</v>
+        <v>1.844757917015912</v>
       </c>
       <c r="F46" t="n">
-        <v>2.306952647332895</v>
+        <v>2.312916051530603</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.2414613409866284</v>
+        <v>-0.2478879180405105</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45721</v>
       </c>
       <c r="B47" t="n">
-        <v>2.978211352724363</v>
+        <v>2.919273997009374</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1.169670833333335</v>
+        <v>1.146512499650754</v>
       </c>
       <c r="F47" t="n">
-        <v>1.687642918468835</v>
+        <v>1.614890562186664</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.6804644686805013</v>
+        <v>-0.5387015962800707</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45722</v>
       </c>
       <c r="B48" t="n">
-        <v>3.545514208741797</v>
+        <v>3.518445688956578</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1.443081083333334</v>
+        <v>1.43049358282887</v>
       </c>
       <c r="F48" t="n">
-        <v>1.767747948622533</v>
+        <v>1.76870589737448</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.5042166342986163</v>
+        <v>-0.5058473564611097</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45723</v>
       </c>
       <c r="B49" t="n">
-        <v>5.540587458529935</v>
+        <v>5.680463909637816</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2.128111166783082</v>
+        <v>2.185291833682578</v>
       </c>
       <c r="F49" t="n">
-        <v>3.552465461738951</v>
+        <v>3.547668716719708</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2278998071133087</v>
+        <v>0.2299834683949712</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45724</v>
       </c>
       <c r="B50" t="n">
-        <v>4.050668669896335</v>
+        <v>3.744370470634418</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1.6647585</v>
+        <v>1.538683499650755</v>
       </c>
       <c r="F50" t="n">
-        <v>1.982892373832983</v>
+        <v>1.899784730263355</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.7546418479769832</v>
+        <v>-0.6106418648253074</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45725</v>
       </c>
       <c r="B51" t="n">
-        <v>2.842203040188159</v>
+        <v>2.88616220722794</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1.161042416783084</v>
+        <v>1.176450749650757</v>
       </c>
       <c r="F51" t="n">
-        <v>1.497503205544778</v>
+        <v>1.474132133810355</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.03488916224929084</v>
+        <v>-0.002838835584501043</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45726</v>
       </c>
       <c r="B52" t="n">
-        <v>3.474737190339291</v>
+        <v>3.616355439628498</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1.396374416783085</v>
+        <v>1.452199417171136</v>
       </c>
       <c r="F52" t="n">
-        <v>1.785794690617619</v>
+        <v>1.799761727393827</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.726352699851303</v>
+        <v>-0.7534625620837356</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45727</v>
       </c>
       <c r="B53" t="n">
-        <v>4.006132589959557</v>
+        <v>3.798217054869502</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>1.581261000000001</v>
+        <v>1.4951511661622</v>
       </c>
       <c r="F53" t="n">
-        <v>1.943211800018978</v>
+        <v>1.910756329925187</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.7343474596563013</v>
+        <v>-0.6768972188496369</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45728</v>
       </c>
       <c r="B54" t="n">
-        <v>5.625609861594322</v>
+        <v>5.495500310465884</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>2.095864416666667</v>
+        <v>2.041467082828868</v>
       </c>
       <c r="F54" t="n">
-        <v>3.053525061457796</v>
+        <v>3.06301177642395</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.3504832232102288</v>
+        <v>-0.3588876415870144</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45729</v>
       </c>
       <c r="B55" t="n">
-        <v>4.923515321300428</v>
+        <v>4.824982413011623</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1.888745832984089</v>
+        <v>1.851791667171134</v>
       </c>
       <c r="F55" t="n">
-        <v>2.266505104022829</v>
+        <v>2.247361375474647</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.1970279695217094</v>
+        <v>-0.176892297374605</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45730</v>
       </c>
       <c r="B56" t="n">
-        <v>4.024469324967254</v>
+        <v>3.952907004027788</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1.498434669072584</v>
+        <v>1.470236187194569</v>
       </c>
       <c r="F56" t="n">
-        <v>1.937255160200157</v>
+        <v>1.92119144627022</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.6305911582745025</v>
+        <v>-0.6036615592727699</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45731</v>
       </c>
       <c r="B57" t="n">
-        <v>4.64124796512622</v>
+        <v>4.739992770118386</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1.866716663911502</v>
+        <v>1.902870833760188</v>
       </c>
       <c r="F57" t="n">
-        <v>2.254897885591962</v>
+        <v>2.292896157944511</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1486461149752455</v>
+        <v>0.1197112804381641</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45732</v>
       </c>
       <c r="B58" t="n">
-        <v>4.999993007216204</v>
+        <v>5.234639979103915</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>1.859328416977106</v>
+        <v>1.9465409161622</v>
       </c>
       <c r="F58" t="n">
-        <v>2.227041638326887</v>
+        <v>2.321791690677007</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.6956802090399905</v>
+        <v>-0.8430358481535511</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45733</v>
       </c>
       <c r="B59" t="n">
-        <v>6.694519331429914</v>
+        <v>6.641633837960513</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>2.433750584225849</v>
+        <v>2.411558916162199</v>
       </c>
       <c r="F59" t="n">
-        <v>2.842018564777006</v>
+        <v>2.85013842343778</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.3056637512816018</v>
+        <v>-0.3131351663693227</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45734</v>
       </c>
       <c r="B60" t="n">
-        <v>3.490302126306223</v>
+        <v>3.21838252079281</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>1.370333917792013</v>
+        <v>1.261867251862644</v>
       </c>
       <c r="F60" t="n">
-        <v>1.619685157193385</v>
+        <v>1.507016291151225</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.3899184735593604</v>
+        <v>-0.2032725708071534</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45735</v>
       </c>
       <c r="B61" t="n">
-        <v>4.93291904167388</v>
+        <v>4.859069111510331</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1.879855903666956</v>
+        <v>1.849863070488844</v>
       </c>
       <c r="F61" t="n">
-        <v>2.281175932527941</v>
+        <v>2.287245634923709</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.6826547253582969</v>
+        <v>-0.6916209789628134</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45736</v>
       </c>
       <c r="B62" t="n">
-        <v>5.454097750573396</v>
+        <v>5.362781518536694</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>1.762760417636794</v>
+        <v>1.735706252716356</v>
       </c>
       <c r="F62" t="n">
-        <v>2.292614773308487</v>
+        <v>2.259311170059259</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.610605118349375</v>
+        <v>-0.5641521668073772</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45737</v>
       </c>
       <c r="B63" t="n">
-        <v>4.562544839864694</v>
+        <v>4.311746947745624</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1.520602044993886</v>
+        <v>1.431618774175583</v>
       </c>
       <c r="F63" t="n">
-        <v>1.860920812701718</v>
+        <v>1.744705980593567</v>
       </c>
       <c r="G63" t="n">
-        <v>0.04650738464216997</v>
+        <v>0.1618803032254763</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45738</v>
       </c>
       <c r="B64" t="n">
-        <v>5.208345619733429</v>
+        <v>5.080324817764987</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1.6242</v>
+        <v>1.581290167326354</v>
       </c>
       <c r="F64" t="n">
-        <v>2.024945774628343</v>
+        <v>2.048824432426304</v>
       </c>
       <c r="G64" t="n">
-        <v>0.2271250637172046</v>
+        <v>0.2087897279498817</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45739</v>
       </c>
       <c r="B65" t="n">
-        <v>4.861875639901254</v>
+        <v>4.812321055670989</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1.840633333061698</v>
+        <v>1.812816665968175</v>
       </c>
       <c r="F65" t="n">
-        <v>2.314534216627715</v>
+        <v>2.264416772670393</v>
       </c>
       <c r="G65" t="n">
-        <v>0.4516362643511618</v>
+        <v>0.475126989519105</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45740</v>
       </c>
       <c r="B66" t="n">
-        <v>2.736878182826903</v>
+        <v>2.712709751713731</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>1.085841667442767</v>
+        <v>1.077647333682578</v>
       </c>
       <c r="F66" t="n">
-        <v>1.430126172274262</v>
+        <v>1.396628328609711</v>
       </c>
       <c r="G66" t="n">
-        <v>0.6996370684684776</v>
+        <v>0.7135430794781703</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45741</v>
       </c>
       <c r="B67" t="n">
-        <v>8.236491784301787</v>
+        <v>7.854994181304383</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>1.845377084691512</v>
+        <v>1.762199417015915</v>
       </c>
       <c r="F67" t="n">
-        <v>3.974766709795524</v>
+        <v>3.974954157264201</v>
       </c>
       <c r="G67" t="n">
-        <v>0.7511153693597508</v>
+        <v>0.7510918943246252</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45742</v>
       </c>
       <c r="B68" t="n">
-        <v>5.697475454674795</v>
+        <v>5.588765954739533</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>1.396335416666667</v>
+        <v>1.369349417171132</v>
       </c>
       <c r="F68" t="n">
-        <v>1.949811617636646</v>
+        <v>1.920424092419523</v>
       </c>
       <c r="G68" t="n">
-        <v>0.916009755590561</v>
+        <v>0.9185224748477745</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45743</v>
       </c>
       <c r="B69" t="n">
-        <v>5.399776280798949</v>
+        <v>5.682536959552183</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1.521299999999998</v>
+        <v>1.619159832828865</v>
       </c>
       <c r="F69" t="n">
-        <v>3.574421481192213</v>
+        <v>3.647740827308366</v>
       </c>
       <c r="G69" t="n">
-        <v>0.6730309638286258</v>
+        <v>0.659479664703828</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45744</v>
       </c>
       <c r="B70" t="n">
-        <v>3.566100475276127</v>
+        <v>3.715272460167259</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>1.224895833333333</v>
+        <v>1.2824806661622</v>
       </c>
       <c r="F70" t="n">
-        <v>1.600162215149346</v>
+        <v>1.674028583099199</v>
       </c>
       <c r="G70" t="n">
-        <v>0.5936049913649251</v>
+        <v>0.5552191493375651</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45745</v>
       </c>
       <c r="B71" t="n">
-        <v>4.81611806266111</v>
+        <v>4.905437541882931</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1.782972166666665</v>
+        <v>1.819327832828868</v>
       </c>
       <c r="F71" t="n">
-        <v>2.435881509885281</v>
+        <v>2.401862479340316</v>
       </c>
       <c r="G71" t="n">
-        <v>-1.781165096949862</v>
+        <v>-1.704025162054732</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45746</v>
       </c>
       <c r="B72" t="n">
-        <v>4.656098785460113</v>
+        <v>4.51237843421992</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>1.782123333333333</v>
+        <v>1.72666083368258</v>
       </c>
       <c r="F72" t="n">
-        <v>2.294532808835747</v>
+        <v>2.191773703755971</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.8958676967009136</v>
+        <v>-0.7298598033591905</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45747</v>
       </c>
       <c r="B73" t="n">
-        <v>4.216960527444166</v>
+        <v>4.181713587313586</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1.693373666899499</v>
+        <v>1.67944600050447</v>
       </c>
       <c r="F73" t="n">
-        <v>2.02888951481646</v>
+        <v>1.990311905560181</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.06848777228090741</v>
+        <v>-0.0282412978781188</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45748</v>
       </c>
       <c r="B74" t="n">
-        <v>2.094800744203067</v>
+        <v>2.01842383984979</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0.8397596666666652</v>
+        <v>0.8106123336825792</v>
       </c>
       <c r="F74" t="n">
-        <v>1.079737658327861</v>
+        <v>1.130416488396319</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.1685370553208216</v>
+        <v>-0.2808048357425021</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45749</v>
       </c>
       <c r="B75" t="n">
-        <v>6.208284581481155</v>
+        <v>6.404179089663477</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>1.374792249999999</v>
+        <v>1.413653583837799</v>
       </c>
       <c r="F75" t="n">
-        <v>3.900309022017505</v>
+        <v>3.950444196426734</v>
       </c>
       <c r="G75" t="n">
-        <v>0.7838460034756011</v>
+        <v>0.7782533348105798</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45750</v>
       </c>
       <c r="B76" t="n">
-        <v>2.608903678095088</v>
+        <v>2.590699479468997</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.5481416666666669</v>
+        <v>0.542980667171134</v>
       </c>
       <c r="F76" t="n">
-        <v>0.6841456478703933</v>
+        <v>0.7022369902827984</v>
       </c>
       <c r="G76" t="n">
-        <v>0.04265660212211331</v>
+        <v>-0.008644242330621221</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45751</v>
       </c>
       <c r="B77" t="n">
-        <v>2.818738488922325</v>
+        <v>3.174691755875113</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0.5812791666666661</v>
+        <v>0.6553166670159124</v>
       </c>
       <c r="F77" t="n">
-        <v>0.767399818923182</v>
+        <v>0.8020005121140669</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.3732159794796839</v>
+        <v>-0.4998393889308657</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45752</v>
       </c>
       <c r="B78" t="n">
-        <v>4.039799477010487</v>
+        <v>3.538070751187183</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0.8402624999999997</v>
+        <v>0.7360431663174221</v>
       </c>
       <c r="F78" t="n">
-        <v>1.001434111869905</v>
+        <v>0.9106276027915735</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.5115080537644374</v>
+        <v>-0.2498195825576301</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45753</v>
       </c>
       <c r="B79" t="n">
-        <v>3.844487558494216</v>
+        <v>4.129225733725262</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.7982666666666663</v>
+        <v>0.8559041663174199</v>
       </c>
       <c r="F79" t="n">
-        <v>1.012218590111181</v>
+        <v>1.059902881288715</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.6473335801793842</v>
+        <v>-0.806196841973728</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45754</v>
       </c>
       <c r="B80" t="n">
-        <v>3.8975841042618</v>
+        <v>3.94114140578645</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.8003249999999998</v>
+        <v>0.8087598329840876</v>
       </c>
       <c r="F80" t="n">
-        <v>1.027920861901992</v>
+        <v>1.023192360341043</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.1016063304256527</v>
+        <v>-0.09149472222564481</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45755</v>
       </c>
       <c r="B81" t="n">
-        <v>5.060937370368344</v>
+        <v>4.745087346733568</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>1.058875</v>
+        <v>0.9891681670159115</v>
       </c>
       <c r="F81" t="n">
-        <v>1.323128103838274</v>
+        <v>1.308618532396234</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.5866708287834661</v>
+        <v>-0.5520624137214964</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45756</v>
       </c>
       <c r="B82" t="n">
-        <v>3.192268696125719</v>
+        <v>3.053505018412177</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0.7005916666666662</v>
+        <v>0.6683734994955316</v>
       </c>
       <c r="F82" t="n">
-        <v>0.8883401502240005</v>
+        <v>0.8939628444389919</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.1147252922151563</v>
+        <v>-0.1288811201348554</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45757</v>
       </c>
       <c r="B83" t="n">
-        <v>3.929034636174562</v>
+        <v>3.712783543821811</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0.8677347826086954</v>
+        <v>0.8199863481905194</v>
       </c>
       <c r="F83" t="n">
-        <v>1.105624265330205</v>
+        <v>1.074975317405097</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.6532898478675766</v>
+        <v>-0.5628988103101984</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>
